--- a/313_class_schedule.xlsx
+++ b/313_class_schedule.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="70" documentId="13_ncr:1_{A2CBACCE-2F31-434D-A06E-D6564BBA565B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE54B737-17FB-5C4C-949B-54EC6F6C61AC}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="38460" yWindow="600" windowWidth="34560" windowHeight="20660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="60" yWindow="660" windowWidth="34560" windowHeight="20660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Syllabus" sheetId="1" r:id="rId1"/>
